--- a/moving_target/Top_Candidates_Analysis.xlsx
+++ b/moving_target/Top_Candidates_Analysis.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,50 +437,60 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Peak Prob.</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Kinematic age</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Global Hit Prob.</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Min Dist (°)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>RA (deg)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>DEC (deg)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Dist (pc)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>V_T (km/s)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>RV (km/s)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Abs Mag (Mg)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Color (BP-RP)0</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Extinction (Av)</t>
         </is>
@@ -489,369 +499,429 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1859461255653506176</t>
+          <t>1859620478681748992</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>0.340645</v>
       </c>
       <c r="C2" t="n">
-        <v>1.867035166134953e-05</v>
+        <v>110000</v>
       </c>
       <c r="D2" t="n">
-        <v>312.6666490989387</v>
+        <v>0.283345</v>
       </c>
       <c r="E2" t="n">
-        <v>30.47393558423438</v>
+        <v>0.1337803705318289</v>
       </c>
       <c r="F2" t="n">
-        <v>824.3090824110753</v>
+        <v>313.1937827597167</v>
       </c>
       <c r="G2" t="n">
-        <v>32.30398960248105</v>
+        <v>31.42029958578744</v>
       </c>
       <c r="H2" t="n">
-        <v>-30.042374</v>
+        <v>585.0306942318194</v>
       </c>
       <c r="I2" t="n">
-        <v>3.339003238525098</v>
+        <v>83.33732275373495</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6826124248804177</v>
+        <v>-26.460108</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2730472150364875</v>
+        <v>5.588544268828327</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.411157094567786</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.2135840044039491</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1858717401682424064</t>
+          <t>1858823538912295424</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.248</v>
+        <v>0.325</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002000805784163628</v>
+        <v>125000</v>
       </c>
       <c r="D3" t="n">
-        <v>312.8205394119935</v>
+        <v>0.001273</v>
       </c>
       <c r="E3" t="n">
-        <v>30.55588420623976</v>
+        <v>0.2202288157374875</v>
       </c>
       <c r="F3" t="n">
-        <v>324.2780531362376</v>
+        <v>313.2701316677835</v>
       </c>
       <c r="G3" t="n">
-        <v>7.104670891292185</v>
+        <v>30.90298679752583</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>375.5046015689003</v>
       </c>
       <c r="I3" t="n">
-        <v>9.905060835185948</v>
+        <v>26.87018305903768</v>
       </c>
       <c r="J3" t="n">
-        <v>1.11397092488491</v>
+        <v>-92.66327</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1153899813600358</v>
+        <v>7.252649023112443</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.454001691942709</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.1534780406081593</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1858708158912839936</t>
+          <t>1858716229139316224</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.159</v>
+        <v>0.121693</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01169711602501377</v>
+        <v>80000</v>
       </c>
       <c r="D4" t="n">
-        <v>312.6071439607677</v>
+        <v>0.001798</v>
       </c>
       <c r="E4" t="n">
-        <v>30.35572924212284</v>
+        <v>0.1639128033781141</v>
       </c>
       <c r="F4" t="n">
-        <v>677.3043317955245</v>
+        <v>312.8331215698268</v>
       </c>
       <c r="G4" t="n">
-        <v>47.24136930646184</v>
+        <v>30.50228862877693</v>
       </c>
       <c r="H4" t="n">
-        <v>-10.221604</v>
+        <v>563.7800825272858</v>
       </c>
       <c r="I4" t="n">
-        <v>3.636215333546115</v>
+        <v>26.34851117644927</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6876707731365563</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.23328113088523</v>
+        <v>8.730141043441064</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.107412868084804</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.2124652623840224</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1859475583664613504</t>
+          <t>1858704207542762368</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.157</v>
+        <v>0.065604</v>
       </c>
       <c r="C5" t="n">
-        <v>0.007038247604840692</v>
+        <v>79000</v>
       </c>
       <c r="D5" t="n">
-        <v>312.6790524574813</v>
+        <v>0.00138</v>
       </c>
       <c r="E5" t="n">
-        <v>30.77895189649519</v>
+        <v>0.1029585890294766</v>
       </c>
       <c r="F5" t="n">
-        <v>752.044295181758</v>
+        <v>312.732656737548</v>
       </c>
       <c r="G5" t="n">
-        <v>14.0077538469571</v>
+        <v>30.28527745520138</v>
       </c>
       <c r="H5" t="n">
-        <v>-63.23599</v>
+        <v>797.8215580108855</v>
       </c>
       <c r="I5" t="n">
-        <v>4.387762322933201</v>
+        <v>38.14457050518385</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7499191708946178</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2534100177614328</v>
+        <v>6.889781851713421</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.466679966965829</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.266766166987336</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1859434592495657984</t>
+          <t>1859566465171758208</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.156</v>
+        <v>0.06</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002558273713346776</v>
+        <v>89000</v>
       </c>
       <c r="D6" t="n">
-        <v>312.3708555778582</v>
+        <v>0.057057</v>
       </c>
       <c r="E6" t="n">
-        <v>30.32783100609764</v>
+        <v>0.1096290767154016</v>
       </c>
       <c r="F6" t="n">
-        <v>739.7121607848319</v>
+        <v>312.8610240858413</v>
       </c>
       <c r="G6" t="n">
-        <v>57.17225576008937</v>
+        <v>30.83056654526711</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>714.3087002266066</v>
       </c>
       <c r="I6" t="n">
-        <v>6.370513224028437</v>
+        <v>52.22291031774308</v>
       </c>
       <c r="J6" t="n">
-        <v>1.176024657276786</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.250137748618354</v>
+        <v>6.096656991523029</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.089697069902414</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.2439588766782812</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1859471288697194496</t>
+          <t>1859540386133259776</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.154</v>
+        <v>0.056</v>
       </c>
       <c r="C7" t="n">
-        <v>0.005845039681162898</v>
+        <v>130000</v>
       </c>
       <c r="D7" t="n">
-        <v>312.7503721177501</v>
+        <v>0.00026</v>
       </c>
       <c r="E7" t="n">
-        <v>30.68760911361713</v>
+        <v>0.2091375920450167</v>
       </c>
       <c r="F7" t="n">
-        <v>465.6302837704126</v>
+        <v>312.4644420471278</v>
       </c>
       <c r="G7" t="n">
-        <v>3.175032801481047</v>
+        <v>30.98457210176579</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.6010396</v>
+        <v>792.010683868471</v>
       </c>
       <c r="I7" t="n">
-        <v>2.015834839648327</v>
+        <v>37.84479422508443</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2862614109413641</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1984126327189241</v>
+        <v>5.105389915870293</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.948827048404878</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2648079219849517</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1859484070520210304</t>
+          <t>1858717401682424064</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.13</v>
+        <v>0.051264</v>
       </c>
       <c r="C8" t="n">
-        <v>0.006374806735248295</v>
+        <v>134000</v>
       </c>
       <c r="D8" t="n">
-        <v>312.4080257567556</v>
+        <v>0.001517</v>
       </c>
       <c r="E8" t="n">
-        <v>30.80009155001774</v>
+        <v>0.1559504369437122</v>
       </c>
       <c r="F8" t="n">
-        <v>553.0494684610942</v>
+        <v>312.8205394119935</v>
       </c>
       <c r="G8" t="n">
-        <v>30.34021459051564</v>
+        <v>30.55588420623976</v>
       </c>
       <c r="H8" t="n">
-        <v>-8.283887999999999</v>
+        <v>324.2780531362376</v>
       </c>
       <c r="I8" t="n">
-        <v>5.947706945745886</v>
+        <v>7.104670891292185</v>
       </c>
       <c r="J8" t="n">
-        <v>1.043189304912614</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2118842327362957</v>
+        <v>9.905060835185948</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.11397092488491</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.1153899813600358</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1858814880255376384</t>
+          <t>1858814880248240384</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.121</v>
+        <v>0.049</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001493775222846679</v>
+        <v>128000</v>
       </c>
       <c r="D9" t="n">
-        <v>313.0632703804467</v>
+        <v>0.000754</v>
       </c>
       <c r="E9" t="n">
-        <v>30.73563538351881</v>
+        <v>0.1875618465401054</v>
       </c>
       <c r="F9" t="n">
-        <v>587.7638859105962</v>
+        <v>313.06355470522</v>
       </c>
       <c r="G9" t="n">
-        <v>21.36068536700013</v>
+        <v>30.73588007594675</v>
       </c>
       <c r="H9" t="n">
-        <v>-18.81752</v>
+        <v>541.4476292410216</v>
       </c>
       <c r="I9" t="n">
-        <v>4.599756075223585</v>
+        <v>19.98412937382351</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8599564259525661</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2137244781452248</v>
+        <v>5.762569535503841</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>0.2111208449093923</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1858814880248240384</t>
+          <t>1858814880255376384</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.119</v>
+        <v>0.048</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001703432013060114</v>
+        <v>129000</v>
       </c>
       <c r="D10" t="n">
-        <v>313.06355470522</v>
+        <v>0.000183</v>
       </c>
       <c r="E10" t="n">
-        <v>30.73588007594675</v>
+        <v>0.2032176524714924</v>
       </c>
       <c r="F10" t="n">
-        <v>541.4476292410216</v>
+        <v>313.0632703804467</v>
       </c>
       <c r="G10" t="n">
-        <v>19.98412937382351</v>
+        <v>30.73563538351881</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>587.7638859105962</v>
       </c>
       <c r="I10" t="n">
-        <v>5.762569535503841</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
+        <v>21.36068536700013</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-18.81752</v>
+      </c>
       <c r="K10" t="n">
-        <v>0.2111208449093923</v>
+        <v>4.599756075223585</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.8599564259525661</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2137244781452248</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1858823538912295424</t>
+          <t>1859459022270525568</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.091</v>
+        <v>0.02</v>
       </c>
       <c r="C11" t="n">
-        <v>0.000219659866529843</v>
+        <v>78000</v>
       </c>
       <c r="D11" t="n">
-        <v>313.2701316677835</v>
+        <v>0.002442</v>
       </c>
       <c r="E11" t="n">
-        <v>30.90298679752583</v>
+        <v>0.1074683406164688</v>
       </c>
       <c r="F11" t="n">
-        <v>375.5046015689003</v>
+        <v>312.5649799990651</v>
       </c>
       <c r="G11" t="n">
-        <v>26.87018305903768</v>
+        <v>30.3760358549512</v>
       </c>
       <c r="H11" t="n">
-        <v>-92.66327</v>
+        <v>825.8550469210617</v>
       </c>
       <c r="I11" t="n">
-        <v>7.252649023112443</v>
+        <v>15.65088716954767</v>
       </c>
       <c r="J11" t="n">
-        <v>1.454001691942709</v>
+        <v>-34.607624</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1534780406081593</v>
+        <v>4.254376104446724</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.6715965537055446</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2734017307550505</v>
       </c>
     </row>
   </sheetData>
@@ -1203,209 +1273,209 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1859461255653506176</t>
+          <t>1859620478681748992</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>1</v>
+        <v>0.05210500000000001</v>
       </c>
       <c r="AP2" t="n">
-        <v>1</v>
+        <v>0.340645</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1</v>
+        <v>0.00286</v>
       </c>
       <c r="AR2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BH2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1858717401682424064</t>
+          <t>1858823538912295424</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1454,197 +1524,197 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0.06900000000000001</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.108</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.265</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.377</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.466</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.582</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.681</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.747</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.802</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.86</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.888</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.907</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.919</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.919</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.922</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.907</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.895</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.804</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.765</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.717</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.681</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.623</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.5639999999999999</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.497</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.339</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.278</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.121</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.00181</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.055</v>
+        <v>0.325</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.04</v>
+        <v>0.030668</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1858708158912839936</t>
+          <t>1858716229139316224</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.995</v>
+        <v>6e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.484</v>
+        <v>0.121693</v>
       </c>
       <c r="M4" t="n">
-        <v>0.004</v>
+        <v>3.6e-05</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -1809,7 +1879,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1859475583664613504</t>
+          <t>1858704207542762368</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1837,13 +1907,13 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.000192</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.065604</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3.7e-05</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -1897,46 +1967,46 @@
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.459</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.078</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2011,7 +2081,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1859434592495657984</t>
+          <t>1859566465171758208</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2069,10 +2139,10 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.00212</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -2135,58 +2205,58 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.041</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.838</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.996</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.715</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.054</v>
+        <v>0</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
@@ -2213,7 +2283,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1859471288697194496</t>
+          <t>1859540386133259776</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2238,52 +2308,52 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.036</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -2394,16 +2464,16 @@
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>0.004908</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
       <c r="BM7" t="n">
         <v>0</v>
@@ -2415,7 +2485,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1859484070520210304</t>
+          <t>1858717401682424064</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2509,37 +2579,37 @@
         <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.284</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.575</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
         <v>0</v>
@@ -2599,25 +2669,25 @@
         <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>6e-06</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>0.0003500000000000001</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>0.006422000000000001</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>0.027896</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>0.051264</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1858814880255376384</t>
+          <t>1858814880248240384</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2735,40 +2805,40 @@
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.432</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
@@ -2792,13 +2862,13 @@
         <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>0.002177</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>0.049</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>0.009776</v>
       </c>
       <c r="BJ9" t="n">
         <v>0</v>
@@ -2819,7 +2889,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1858814880248240384</t>
+          <t>1858814880255376384</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -2931,40 +3001,40 @@
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.998</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.999</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.08500000000000001</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
@@ -2997,13 +3067,13 @@
         <v>0</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>0.0006500000000000001</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
@@ -3021,7 +3091,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1858823538912295424</t>
+          <t>1859459022270525568</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -3046,10 +3116,10 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -3142,28 +3212,28 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.862</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
         <v>0</v>

--- a/moving_target/Top_Candidates_Analysis.xlsx
+++ b/moving_target/Top_Candidates_Analysis.xlsx
@@ -452,7 +452,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Min Dist (°)</t>
+          <t>Min Dist (pc)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -503,16 +503,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.340645</v>
+        <v>0.033916</v>
       </c>
       <c r="C2" t="n">
-        <v>110000</v>
+        <v>94000</v>
       </c>
       <c r="D2" t="n">
-        <v>0.283345</v>
+        <v>0.11001</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1337803705318289</v>
+        <v>101.2587779385055</v>
       </c>
       <c r="F2" t="n">
         <v>313.1937827597167</v>
@@ -542,386 +542,388 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1858823538912295424</t>
+          <t>1859435795086473728</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.325</v>
+        <v>0.027104</v>
       </c>
       <c r="C3" t="n">
-        <v>125000</v>
+        <v>112000</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001273</v>
+        <v>0.01573</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2202288157374875</v>
+        <v>117.7179741912588</v>
       </c>
       <c r="F3" t="n">
-        <v>313.2701316677835</v>
+        <v>312.4060423773184</v>
       </c>
       <c r="G3" t="n">
-        <v>30.90298679752583</v>
+        <v>30.32136031540005</v>
       </c>
       <c r="H3" t="n">
-        <v>375.5046015689003</v>
+        <v>802.0794219881553</v>
       </c>
       <c r="I3" t="n">
-        <v>26.87018305903768</v>
+        <v>61.71041810089829</v>
       </c>
       <c r="J3" t="n">
-        <v>-92.66327</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>7.252649023112443</v>
+        <v>7.867511033931546</v>
       </c>
       <c r="L3" t="n">
-        <v>1.454001691942709</v>
+        <v>1.710325268357135</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1534780406081593</v>
+        <v>0.2676809174595028</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1858716229139316224</t>
+          <t>1858821511685252224</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.121693</v>
+        <v>0.008303999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>80000</v>
+        <v>85000</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001798</v>
+        <v>7.500000000000001e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1639128033781141</v>
+        <v>130.8840232133211</v>
       </c>
       <c r="F4" t="n">
-        <v>312.8331215698268</v>
+        <v>313.1128443703208</v>
       </c>
       <c r="G4" t="n">
-        <v>30.50228862877693</v>
+        <v>30.82112002113497</v>
       </c>
       <c r="H4" t="n">
-        <v>563.7800825272858</v>
+        <v>821.9437937023158</v>
       </c>
       <c r="I4" t="n">
-        <v>26.34851117644927</v>
+        <v>51.77076002257719</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>8.730141043441064</v>
+        <v>6.914441300861093</v>
       </c>
       <c r="L4" t="n">
-        <v>2.107412868084804</v>
+        <v>1.425038153450123</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2124652623840224</v>
+        <v>0.272504814469865</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1858704207542762368</t>
+          <t>1859481046863208192</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.065604</v>
+        <v>0.006006</v>
       </c>
       <c r="C5" t="n">
-        <v>79000</v>
+        <v>89000</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00138</v>
+        <v>0.000231</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1029585890294766</v>
+        <v>141.6115044928333</v>
       </c>
       <c r="F5" t="n">
-        <v>312.732656737548</v>
+        <v>312.3083095198912</v>
       </c>
       <c r="G5" t="n">
-        <v>30.28527745520138</v>
+        <v>30.64369084822177</v>
       </c>
       <c r="H5" t="n">
-        <v>797.8215580108855</v>
+        <v>828.9059883916279</v>
       </c>
       <c r="I5" t="n">
-        <v>38.14457050518385</v>
+        <v>60.67574972533508</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6.889781851713421</v>
+        <v>7.856630510495868</v>
       </c>
       <c r="L5" t="n">
-        <v>1.466679966965829</v>
+        <v>1.862808545259341</v>
       </c>
       <c r="M5" t="n">
-        <v>0.266766166987336</v>
+        <v>0.2740681627540033</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1859566465171758208</t>
+          <t>1858810654007509248</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.06</v>
+        <v>0.002588</v>
       </c>
       <c r="C6" t="n">
-        <v>89000</v>
+        <v>116000</v>
       </c>
       <c r="D6" t="n">
-        <v>0.057057</v>
+        <v>0.000315</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1096290767154016</v>
+        <v>5.998902073039034</v>
       </c>
       <c r="F6" t="n">
-        <v>312.8610240858413</v>
+        <v>313.1447355108772</v>
       </c>
       <c r="G6" t="n">
-        <v>30.83056654526711</v>
+        <v>30.67060787430072</v>
       </c>
       <c r="H6" t="n">
-        <v>714.3087002266066</v>
+        <v>683.8234836900268</v>
       </c>
       <c r="I6" t="n">
-        <v>52.22291031774308</v>
+        <v>32.9802237178611</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>6.096656991523029</v>
+        <v>6.514812017374858</v>
       </c>
       <c r="L6" t="n">
-        <v>1.089697069902414</v>
+        <v>1.020618684681628</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2439588766782812</v>
+        <v>0.2350198645516126</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1859540386133259776</t>
+          <t>1858707334279082496</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.056</v>
+        <v>0.002</v>
       </c>
       <c r="C7" t="n">
-        <v>130000</v>
+        <v>82000</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00026</v>
+        <v>0.000138</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2091375920450167</v>
+        <v>6.730010924590166</v>
       </c>
       <c r="F7" t="n">
-        <v>312.4644420471278</v>
+        <v>312.6326087341507</v>
       </c>
       <c r="G7" t="n">
-        <v>30.98457210176579</v>
+        <v>30.33781768929849</v>
       </c>
       <c r="H7" t="n">
-        <v>792.010683868471</v>
+        <v>685.1750962899005</v>
       </c>
       <c r="I7" t="n">
-        <v>37.84479422508443</v>
+        <v>59.33844809080631</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-12.862263</v>
       </c>
       <c r="K7" t="n">
-        <v>5.105389915870293</v>
+        <v>2.756559401782267</v>
       </c>
       <c r="L7" t="n">
-        <v>0.948827048404878</v>
+        <v>0.6559607650625914</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2648079219849517</v>
+        <v>0.2353803553592112</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1858717401682424064</t>
+          <t>1858707845362683776</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.051264</v>
+        <v>5.800000000000001e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>134000</v>
+        <v>78000</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001517</v>
+        <v>0.0007199999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1559504369437122</v>
+        <v>134.2040960863698</v>
       </c>
       <c r="F8" t="n">
-        <v>312.8205394119935</v>
+        <v>312.6606228715822</v>
       </c>
       <c r="G8" t="n">
-        <v>30.55588420623976</v>
+        <v>30.36015179716926</v>
       </c>
       <c r="H8" t="n">
-        <v>324.2780531362376</v>
+        <v>818.0249323565017</v>
       </c>
       <c r="I8" t="n">
-        <v>7.104670891292185</v>
+        <v>63.81085558141876</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>9.905060835185948</v>
+        <v>7.777440260305471</v>
       </c>
       <c r="L8" t="n">
-        <v>1.11397092488491</v>
+        <v>1.643852670358992</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1153899813600358</v>
+        <v>0.2716041404555811</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1858814880248240384</t>
+          <t>1859462831894292096</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.049</v>
+        <v>2e-05</v>
       </c>
       <c r="C9" t="n">
-        <v>128000</v>
+        <v>134000</v>
       </c>
       <c r="D9" t="n">
-        <v>0.000754</v>
+        <v>0.006160000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1875618465401054</v>
+        <v>120.9966218949417</v>
       </c>
       <c r="F9" t="n">
-        <v>313.06355470522</v>
+        <v>312.6287856733549</v>
       </c>
       <c r="G9" t="n">
-        <v>30.73588007594675</v>
+        <v>30.54486791865365</v>
       </c>
       <c r="H9" t="n">
-        <v>541.4476292410216</v>
+        <v>557.16444840703</v>
       </c>
       <c r="I9" t="n">
-        <v>19.98412937382351</v>
+        <v>13.11872891403568</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>5.762569535503841</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
+        <v>8.362313140003117</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.9129448764709309</v>
+      </c>
       <c r="M9" t="n">
-        <v>0.2111208449093923</v>
+        <v>0.2121085176797487</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1858814880255376384</t>
+          <t>1858716332218575616</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.048</v>
+        <v>2e-06</v>
       </c>
       <c r="C10" t="n">
-        <v>129000</v>
+        <v>118000</v>
       </c>
       <c r="D10" t="n">
-        <v>0.000183</v>
+        <v>0.000125</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2032176524714924</v>
+        <v>107.1328192268316</v>
       </c>
       <c r="F10" t="n">
-        <v>313.0632703804467</v>
+        <v>312.8849602344176</v>
       </c>
       <c r="G10" t="n">
-        <v>30.73563538351881</v>
+        <v>30.51675276528495</v>
       </c>
       <c r="H10" t="n">
-        <v>587.7638859105962</v>
+        <v>795.297138659627</v>
       </c>
       <c r="I10" t="n">
-        <v>21.36068536700013</v>
+        <v>31.40022751375808</v>
       </c>
       <c r="J10" t="n">
-        <v>-18.81752</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>4.599756075223585</v>
+        <v>7.782809498568363</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8599564259525661</v>
+        <v>1.691571998138489</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2137244781452248</v>
+        <v>0.2659154461736736</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1859459022270525568</t>
+          <t>1858708227632342144</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>78000</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.002442</v>
+        <v>0.000111</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1074683406164688</v>
+        <v>3.150003048409262</v>
       </c>
       <c r="F11" t="n">
-        <v>312.5649799990651</v>
+        <v>312.5695639332984</v>
       </c>
       <c r="G11" t="n">
-        <v>30.3760358549512</v>
+        <v>30.34251957128277</v>
       </c>
       <c r="H11" t="n">
-        <v>825.8550469210617</v>
+        <v>687.8400194968178</v>
       </c>
       <c r="I11" t="n">
-        <v>15.65088716954767</v>
+        <v>41.49419439720614</v>
       </c>
       <c r="J11" t="n">
-        <v>-34.607624</v>
+        <v>-16.484322</v>
       </c>
       <c r="K11" t="n">
-        <v>4.254376104446724</v>
+        <v>3.539677406393071</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6715965537055446</v>
+        <v>0.592146266926127</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2734017307550505</v>
+        <v>0.2360869480817909</v>
       </c>
     </row>
   </sheetData>
@@ -1331,40 +1333,40 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>8e-06</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>0.000255</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.00144</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>0.007708</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>0.015296</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>0.024386</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>0.033916</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>0.02261</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>0.010927</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>0.00341</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>0.000342</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.6e-05</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1394,13 +1396,13 @@
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.05210500000000001</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.340645</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.00286</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1475,7 +1477,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1858823538912295424</t>
+          <t>1859435795086473728</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1581,58 +1583,58 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>2.8e-05</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>0.000195</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>0.001064</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>0.00294</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>0.005838000000000001</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>0.013612</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>0.020235</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>0.025986</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>0.027104</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>0.02268</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>0.017886</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>0.010404</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>0.00429</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>0.001424</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>0.000408</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>0.000189</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>4e-05</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
       <c r="BB3" t="n">
         <v>0</v>
@@ -1641,13 +1643,13 @@
         <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.00181</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.325</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.030668</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1677,7 +1679,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1858716229139316224</t>
+          <t>1858821511685252224</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1708,31 +1710,31 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>6e-05</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.121693</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.6e-05</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>8.500000000000001e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.001732</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.007578999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>0.008303999999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.003549</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.0009840000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1879,7 +1881,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1858704207542762368</t>
+          <t>1859481046863208192</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1907,13 +1909,13 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.000192</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.065604</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>3.7e-05</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -1934,22 +1936,22 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.000114</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.0026</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.006006</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.002299</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.00015</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3e-06</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -2081,7 +2083,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1859566465171758208</t>
+          <t>1858810654007509248</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -2139,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.00212</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -2214,25 +2216,25 @@
         <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.1e-05</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>0.000844</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>0.002304</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>0.002588</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>0.000674</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>8.999999999999999e-05</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.1e-05</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -2283,7 +2285,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1859540386133259776</t>
+          <t>1858707334279082496</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2323,7 +2325,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -2464,16 +2466,16 @@
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.004908</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.056</v>
+        <v>0</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="BL7" t="n">
-        <v>2e-06</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
         <v>0</v>
@@ -2485,7 +2487,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1858717401682424064</t>
+          <t>1858707845362683776</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2513,13 +2515,13 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>5.800000000000001e-05</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>8e-06</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -2669,25 +2671,25 @@
         <v>0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>6e-06</v>
+        <v>0</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.0003500000000000001</v>
+        <v>0</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.006422000000000001</v>
+        <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.027896</v>
+        <v>0</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.051264</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1858814880248240384</t>
+          <t>1859462831894292096</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2862,34 +2864,34 @@
         <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.002177</v>
+        <v>0</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.049</v>
+        <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.009776</v>
+        <v>0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>3e-06</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>3e-06</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>8e-06</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>1.5e-05</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>2e-05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1858814880255376384</t>
+          <t>1858716332218575616</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -3037,10 +3039,10 @@
         <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
@@ -3067,13 +3069,13 @@
         <v>0</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.0006500000000000001</v>
+        <v>0</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.048</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
@@ -3091,7 +3093,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1859459022270525568</t>
+          <t>1858708227632342144</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -3116,10 +3118,10 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
